--- a/assistente_administrativo/fdmdt/chamada.xlsx
+++ b/assistente_administrativo/fdmdt/chamada.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="80">
   <si>
     <t xml:space="preserve">Nome</t>
   </si>
@@ -490,8 +490,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7.45"/>
@@ -499,7 +499,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="6.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="7.2"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -533,6 +533,12 @@
       <c r="J1" s="3" t="n">
         <v>45792</v>
       </c>
+      <c r="K1" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="L1" s="3" t="n">
+        <v>45813</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -565,6 +571,12 @@
       <c r="J2" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -597,6 +609,12 @@
       <c r="J3" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K3" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -629,6 +647,12 @@
       <c r="J4" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K4" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
@@ -661,6 +685,12 @@
       <c r="J5" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K5" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L5" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
@@ -693,6 +723,12 @@
       <c r="J6" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K6" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L6" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
@@ -725,6 +761,12 @@
       <c r="J7" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K7" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
@@ -757,6 +799,12 @@
       <c r="J8" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K8" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L8" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -789,6 +837,12 @@
       <c r="J9" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K9" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L9" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
@@ -821,6 +875,12 @@
       <c r="J10" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K10" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
@@ -853,6 +913,12 @@
       <c r="J11" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K11" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
@@ -885,6 +951,12 @@
       <c r="J12" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K12" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L12" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -917,6 +989,12 @@
       <c r="J13" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K13" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L13" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
@@ -949,6 +1027,12 @@
       <c r="J14" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K14" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L14" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -981,6 +1065,12 @@
       <c r="J15" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K15" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
@@ -1013,6 +1103,12 @@
       <c r="J16" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K16" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -1045,6 +1141,12 @@
       <c r="J17" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K17" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L17" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
@@ -1077,6 +1179,12 @@
       <c r="J18" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K18" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L18" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
@@ -1109,6 +1217,12 @@
       <c r="J19" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K19" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L19" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
@@ -1141,6 +1255,12 @@
       <c r="J20" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K20" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L20" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
@@ -1173,6 +1293,12 @@
       <c r="J21" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K21" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L21" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
@@ -1205,6 +1331,12 @@
       <c r="J22" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K22" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L22" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
@@ -1237,6 +1369,12 @@
       <c r="J23" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K23" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L23" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
@@ -1269,6 +1407,12 @@
       <c r="J24" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K24" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L24" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
@@ -1301,6 +1445,12 @@
       <c r="J25" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="K25" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L25" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
@@ -1332,6 +1482,12 @@
       </c>
       <c r="J26" s="0" t="s">
         <v>2</v>
+      </c>
+      <c r="K26" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L26" s="0" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1351,7 +1507,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="12.73046875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15.71"/>
@@ -1660,17 +1816,17 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/assistente_administrativo/fdmdt/chamada.xlsx
+++ b/assistente_administrativo/fdmdt/chamada.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Chamada" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Usuários" sheetId="2" state="visible" r:id="rId3"/>
     <sheet name="Custos" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Pesquisa" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="88">
   <si>
     <t xml:space="preserve">Nome</t>
   </si>
@@ -262,6 +263,30 @@
   </si>
   <si>
     <t xml:space="preserve">Orégano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hipótese:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">São Paulo futebol clube é o maior time do Brasil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sociais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enquete no google forms peguntando a opinião.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pergunta aberta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pergunta fechada (alternativas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultados de uma – Enquete tipo Brain Storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segundo nuvem de palavras realizada no dia 05 de Junho na sala de aula de assistente administrativo Grimaldi. O maior time do brasil é o Corinthians.</t>
   </si>
 </sst>
 </file>
@@ -368,7 +393,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -410,6 +435,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -490,8 +519,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7.45"/>
@@ -500,6 +529,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="6.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="7.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -539,6 +569,9 @@
       <c r="L1" s="3" t="n">
         <v>45813</v>
       </c>
+      <c r="M1" s="3" t="n">
+        <v>45820</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -577,6 +610,9 @@
       <c r="L2" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M2" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -615,6 +651,9 @@
       <c r="L3" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M3" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -653,6 +692,9 @@
       <c r="L4" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M4" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
@@ -691,6 +733,9 @@
       <c r="L5" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M5" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
@@ -729,6 +774,9 @@
       <c r="L6" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M6" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
@@ -767,6 +815,9 @@
       <c r="L7" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M7" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
@@ -805,6 +856,9 @@
       <c r="L8" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M8" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -843,6 +897,9 @@
       <c r="L9" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M9" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
@@ -881,6 +938,9 @@
       <c r="L10" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M10" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
@@ -919,6 +979,9 @@
       <c r="L11" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M11" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
@@ -957,6 +1020,9 @@
       <c r="L12" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M12" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -995,6 +1061,9 @@
       <c r="L13" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M13" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
@@ -1033,6 +1102,9 @@
       <c r="L14" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M14" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -1071,6 +1143,9 @@
       <c r="L15" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M15" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
@@ -1109,6 +1184,9 @@
       <c r="L16" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M16" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -1147,6 +1225,9 @@
       <c r="L17" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M17" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
@@ -1185,6 +1266,9 @@
       <c r="L18" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M18" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
@@ -1223,6 +1307,9 @@
       <c r="L19" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M19" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
@@ -1261,6 +1348,9 @@
       <c r="L20" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M20" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
@@ -1299,6 +1389,9 @@
       <c r="L21" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M21" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
@@ -1337,6 +1430,9 @@
       <c r="L22" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M22" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
@@ -1375,6 +1471,9 @@
       <c r="L23" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M23" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
@@ -1413,6 +1512,9 @@
       <c r="L24" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M24" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
@@ -1451,6 +1553,9 @@
       <c r="L25" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="M25" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
@@ -1488,6 +1593,9 @@
       </c>
       <c r="L26" s="0" t="s">
         <v>8</v>
+      </c>
+      <c r="M26" s="0" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1507,7 +1615,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15.71"/>
@@ -1816,15 +1924,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6.42"/>
   </cols>
@@ -2277,4 +2383,61 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>